--- a/mappingCorps/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRPregnancyHistoryLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping Métier/CDA/FHIR : "Historique de la grossesse"</t>
+    <t>Mapping Métier/CDA/FHIR : "Historique de la grossesse "</t>
   </si>
   <si>
     <t>Status</t>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMHistoriqueGrossesse vers le profil CDA FRCDAHistoriqueDeLaGrossesse, puis vers le profil FHIR FRPregnancyHistoryDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMPregnancyHistory vers le profil CDA FRCDAHistoriqueDeLaGrossesse, puis vers le profil FHIR FRPregnancyHistoryDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-historique-grossesse</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-pregnancy-history</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-historique-de-la-grossesse</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse</t>
+    <t>FRLMPregnancyHistory</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,36 +118,33 @@
     <t>FRCDAHistoriqueDeLaGrossesse</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.id</t>
-  </si>
-  <si>
-    <t>FRLMHistoriqueGrossesse.code</t>
+    <t>FRLMPregnancyHistory.header.status</t>
+  </si>
+  <si>
+    <t>FRCDAHistoriqueDeLaGrossesse.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMPregnancyHistory.type</t>
   </si>
   <si>
     <t>FRCDAHistoriqueDeLaGrossesse.code</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse.statut</t>
-  </si>
-  <si>
-    <t>FRCDAHistoriqueDeLaGrossesse.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMHistoriqueGrossesse.periodeGrossesse</t>
+    <t>FRLMPregnancyHistory.observationDate[x]</t>
   </si>
   <si>
     <t>FRCDAHistoriqueDeLaGrossesse.effectiveTime</t>
   </si>
   <si>
-    <t>FRLMHistoriqueGrossesse.choice[x]</t>
+    <t>FRLMPregnancyHistory.result</t>
   </si>
   <si>
     <t>FRCDAHistoriqueDeLaGrossesse.entryRelationship:frObservationSurLaGrossesse</t>
   </si>
   <si>
+    <t>FRLMPregnancyHistory.component</t>
+  </si>
+  <si>
     <t>FRCDAHistoriqueDeLaGrossesse.entryRelationship:frNaissance</t>
   </si>
   <si>
@@ -157,19 +154,22 @@
     <t>FRPregnancyHistoryDocument</t>
   </si>
   <si>
+    <t>FRLMPregnancyHistory.header.identifier</t>
+  </si>
+  <si>
     <t>FRPregnancyHistoryDocument.identifier</t>
   </si>
   <si>
     <t>FRPregnancyHistoryDocument.code</t>
   </si>
   <si>
-    <t>FRPregnancyHistoryDocument.date</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.entry.item:FRObservationPregnancyDocument</t>
-  </si>
-  <si>
-    <t>FRPregnancyHistoryDocument.entry.item:FRObservationBirthEventDocument</t>
+    <t>FRPregnancyHistoryDocument.effective[x]</t>
+  </si>
+  <si>
+    <t>FRPregnancyHistoryDocument.hasMember:FRObservationPregnancyDocument</t>
+  </si>
+  <si>
+    <t>FRPregnancyHistoryDocument.component</t>
   </si>
 </sst>
 </file>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -535,19 +535,6 @@
         <v>43</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -578,7 +565,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -587,7 +574,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -595,20 +582,20 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -621,7 +608,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -634,7 +621,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
@@ -647,7 +634,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
@@ -660,7 +647,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
